--- a/data/baidu/china_musical.xlsx
+++ b/data/baidu/china_musical.xlsx
@@ -580,24 +580,30 @@
           <t>https://movie.douban.com/subject/34841525/</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>850.7142857142857</v>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>永不消逝的电波(舞剧)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>永不消逝的电波</t>
+        </is>
+      </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -660,16 +666,24 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>黑暗中的舞者</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>黑暗中的舞者</t>
+        </is>
+      </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
@@ -737,16 +751,24 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>丝路花雨</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>丝路花雨</t>
+        </is>
+      </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
@@ -814,16 +836,24 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>杨贵妃</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>杨贵妃</t>
+        </is>
+      </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -888,24 +918,30 @@
           <t>https://movie.douban.com/subject/36401998/</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>4267</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>只此青绿</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>只此青绿</t>
+        </is>
+      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -965,24 +1001,30 @@
           <t>https://movie.douban.com/subject/35512640/</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>7038.428571428572</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>伟大征程——庆祝中国共产党成立100周年文艺演出</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>伟大征程</t>
+        </is>
+      </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1045,16 +1087,24 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>东方红</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>东方红</t>
+        </is>
+      </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
@@ -1122,16 +1172,24 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>五朵金花</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>五朵金花</t>
+        </is>
+      </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
@@ -1199,16 +1257,24 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>洞</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>洞</t>
+        </is>
+      </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
@@ -1276,16 +1342,24 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>我和春天有个约会</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>我和春天有个约会</t>
+        </is>
+      </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
@@ -1353,16 +1427,24 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>如果·爱</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>如果</t>
+        </is>
+      </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
@@ -1430,16 +1512,24 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>阿诗玛</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>阿诗玛</t>
+        </is>
+      </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
@@ -1507,16 +1597,24 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>智取威虎山</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>智取威虎山</t>
+        </is>
+      </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
@@ -1584,16 +1682,24 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>大路</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>大路</t>
+        </is>
+      </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
@@ -1661,16 +1767,24 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>92黑玫瑰对黑玫瑰</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>92黑玫瑰对黑玫瑰</t>
+        </is>
+      </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
@@ -1738,16 +1852,24 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>小美人鱼2：重返大海</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>小美人鱼2</t>
+        </is>
+      </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
@@ -1815,16 +1937,24 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>上海之夜</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>上海之夜</t>
+        </is>
+      </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
@@ -1892,16 +2022,24 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>野玫瑰之恋</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>野玫瑰之恋</t>
+        </is>
+      </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
@@ -1969,16 +2107,24 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>天下无双</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>天下无双</t>
+        </is>
+      </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
@@ -2046,16 +2192,24 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>金玉良缘红楼梦</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>金玉良缘红楼梦</t>
+        </is>
+      </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
@@ -2120,24 +2274,30 @@
           <t>https://movie.douban.com/subject/21360412/</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>361.7142857142857</v>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>狂舞派</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>狂舞派</t>
+        </is>
+      </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -2200,16 +2360,24 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>天边一朵云</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>天边一朵云</t>
+        </is>
+      </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
@@ -2277,16 +2445,24 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>孔雀公主</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>孔雀公主</t>
+        </is>
+      </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
@@ -2354,16 +2530,24 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>柠檬可乐</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>柠檬可乐</t>
+        </is>
+      </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
@@ -2431,16 +2615,24 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>红色娘子军</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>红色娘子军</t>
+        </is>
+      </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
@@ -2508,16 +2700,24 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1983年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1983年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
@@ -2582,24 +2782,30 @@
           <t>https://movie.douban.com/subject/10833924/</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>25681.57142857143</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>天台爱情</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>天台爱情</t>
+        </is>
+      </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -2662,16 +2868,24 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4184567707, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>更好的我</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>更好的我</t>
+        </is>
+      </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
@@ -2739,16 +2953,24 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>爱君如梦</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>爱君如梦</t>
+        </is>
+      </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
@@ -2816,16 +3038,24 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>玫瑰玫瑰我爱你</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>玫瑰玫瑰我爱你</t>
+        </is>
+      </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
@@ -2893,16 +3123,24 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4184789554, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>不要再见啊，鱼花塘</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>不要再见啊，鱼花塘</t>
+        </is>
+      </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
@@ -2970,16 +3208,24 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1998年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1998年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
@@ -3047,16 +3293,24 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4185066570, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>致埃文·汉森</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>致埃文</t>
+        </is>
+      </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
@@ -3124,16 +3378,24 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4185256687, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>只有大海知道</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>只有大海知道</t>
+        </is>
+      </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
@@ -3201,16 +3463,24 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>芭啦芭啦樱之花</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>芭啦芭啦樱之花</t>
+        </is>
+      </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
@@ -3278,16 +3548,24 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1999年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1999年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
@@ -3352,24 +3630,30 @@
           <t>https://movie.douban.com/subject/26733890/</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>1465.857142857143</v>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>元宵喜乐会</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>元宵喜乐会</t>
+        </is>
+      </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -3429,24 +3713,30 @@
           <t>https://movie.douban.com/subject/36466154/</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>1002.428571428571</v>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>永不消逝的电波</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>永不消逝的电波</t>
+        </is>
+      </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -3509,16 +3799,24 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>莫文蔚：好莫文蔚巡回演唱</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>莫文蔚</t>
+        </is>
+      </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
@@ -3586,16 +3884,24 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1984年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1984年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
@@ -3663,16 +3969,24 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4185958245, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2020年央视中秋晚会‎</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2020年央视中秋晚会‎</t>
+        </is>
+      </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
@@ -3740,16 +4054,24 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2009年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2009年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
@@ -3814,24 +4136,30 @@
           <t>https://movie.douban.com/subject/25782827/</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>636.1428571428571</v>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>半熟少女</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>半熟少女</t>
+        </is>
+      </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -3894,16 +4222,24 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>仙乐飘飘</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>仙乐飘飘</t>
+        </is>
+      </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
@@ -3971,16 +4307,24 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2000年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2000年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
@@ -4045,24 +4389,30 @@
           <t>https://movie.douban.com/subject/11776289/</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>11438.14285714286</v>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>华丽上班族</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>华丽上班族</t>
+        </is>
+      </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -4125,16 +4475,24 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2005年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2005年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
@@ -4202,16 +4560,24 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1990年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1990年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
@@ -4276,21 +4642,27 @@
           <t>https://movie.douban.com/subject/30141681/</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>飞奔去月球</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>飞奔去月球</t>
+        </is>
+      </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -4356,16 +4728,24 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1995年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1995年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
@@ -4433,16 +4813,24 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2008年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2008年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T52" t="n">
         <v>0</v>
       </c>
@@ -4510,16 +4898,24 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>虫不知</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>虫不知</t>
+        </is>
+      </c>
       <c r="T53" t="n">
         <v>0</v>
       </c>
@@ -4587,16 +4983,24 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2001年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2001年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T54" t="n">
         <v>0</v>
       </c>
@@ -4664,16 +5068,24 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1996年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1996年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
@@ -4741,16 +5153,24 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>千娇百媚</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>千娇百媚</t>
+        </is>
+      </c>
       <c r="T56" t="n">
         <v>0</v>
       </c>
@@ -4815,24 +5235,30 @@
           <t>https://movie.douban.com/subject/26594013/</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>539.7142857142857</v>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>2014年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>2014年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -4895,16 +5321,24 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>2010年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>2010年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T58" t="n">
         <v>0</v>
       </c>
@@ -4972,16 +5406,24 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1997年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1997年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T59" t="n">
         <v>0</v>
       </c>
@@ -5049,16 +5491,24 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2002年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2002年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T60" t="n">
         <v>0</v>
       </c>
@@ -5126,16 +5576,24 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1989年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1989年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T61" t="n">
         <v>0</v>
       </c>
@@ -5203,16 +5661,24 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1993年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1993年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
@@ -5280,16 +5746,24 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2003年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>2003年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
@@ -5357,16 +5831,24 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>2006年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>2006年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T64" t="n">
         <v>0</v>
       </c>
@@ -5431,24 +5913,30 @@
           <t>https://movie.douban.com/subject/26594010/</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>488.8571428571428</v>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>2013年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>2013年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -5511,16 +5999,24 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1986年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1986年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T66" t="n">
         <v>0</v>
       </c>
@@ -5585,24 +6081,30 @@
           <t>https://movie.douban.com/subject/26594009/</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>372.8571428571428</v>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2012年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2012年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -5665,16 +6167,24 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>六月新娘</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>六月新娘</t>
+        </is>
+      </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
@@ -5742,16 +6252,24 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4188005965, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>东方卫视梦圆东方2016跨年盛典</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>东方卫视梦圆东方2016跨年盛典</t>
+        </is>
+      </c>
       <c r="T69" t="n">
         <v>0</v>
       </c>
@@ -5819,16 +6337,24 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>2004年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>2004年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
@@ -5896,16 +6422,24 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>宝莲灯</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>宝莲灯</t>
+        </is>
+      </c>
       <c r="T71" t="n">
         <v>0</v>
       </c>
@@ -5973,16 +6507,24 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1992年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1992年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T72" t="n">
         <v>0</v>
       </c>
@@ -6050,16 +6592,24 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1987年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1987年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T73" t="n">
         <v>0</v>
       </c>
@@ -6127,16 +6677,24 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1991年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1991年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T74" t="n">
         <v>0</v>
       </c>
@@ -6204,16 +6762,24 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2007年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>2007年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T75" t="n">
         <v>0</v>
       </c>
@@ -6281,16 +6847,24 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>蛇王子</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>蛇王子</t>
+        </is>
+      </c>
       <c r="T76" t="n">
         <v>0</v>
       </c>
@@ -6358,16 +6932,24 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>曼波女郎</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>曼波女郎</t>
+        </is>
+      </c>
       <c r="T77" t="n">
         <v>0</v>
       </c>
@@ -6435,16 +7017,24 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4188170020, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>狂舞派3</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>狂舞派3</t>
+        </is>
+      </c>
       <c r="T78" t="n">
         <v>0</v>
       </c>
@@ -6512,16 +7102,24 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1988年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1988年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T79" t="n">
         <v>0</v>
       </c>
@@ -6586,24 +7184,30 @@
           <t>https://movie.douban.com/subject/26594007/</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>569.4285714285714</v>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2011年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>2011年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -6666,16 +7270,24 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>小煞星</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>小煞星</t>
+        </is>
+      </c>
       <c r="T81" t="n">
         <v>0</v>
       </c>
@@ -6743,16 +7355,24 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>万古流芳</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>万古流芳</t>
+        </is>
+      </c>
       <c r="T82" t="n">
         <v>0</v>
       </c>
@@ -6817,24 +7437,30 @@
           <t>https://movie.douban.com/subject/26274911/</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>126.2857142857143</v>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>中美舞林冠军对抗赛</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>中美舞林冠军对抗赛</t>
+        </is>
+      </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -6897,16 +7523,24 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>乔太守乱点鸳鸯谱</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>乔太守乱点鸳鸯谱</t>
+        </is>
+      </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
@@ -6974,16 +7608,24 @@
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1994年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1994年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T85" t="n">
         <v>0</v>
       </c>
@@ -7051,16 +7693,24 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1985年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1985年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
@@ -7128,16 +7778,24 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4188903457, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>52赫兹，我爱你</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>52赫兹，我爱你</t>
+        </is>
+      </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
@@ -7202,24 +7860,30 @@
           <t>https://movie.douban.com/subject/26891314/</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>1423.857142857143</v>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>小戏骨：花木兰</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -7282,16 +7946,24 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>西部舞狂</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>西部舞狂</t>
+        </is>
+      </c>
       <c r="T89" t="n">
         <v>0</v>
       </c>
@@ -7359,16 +8031,24 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>江姐</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>江姐</t>
+        </is>
+      </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
@@ -7436,16 +8116,24 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>香江花月夜</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>香江花月夜</t>
+        </is>
+      </c>
       <c r="T91" t="n">
         <v>0</v>
       </c>
@@ -7513,16 +8201,24 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>万花迎春</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>万花迎春</t>
+        </is>
+      </c>
       <c r="T92" t="n">
         <v>0</v>
       </c>
@@ -7590,16 +8286,24 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4189439859, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>2017年辽宁卫视春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>2017年辽宁卫视春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T93" t="n">
         <v>0</v>
       </c>
@@ -7667,16 +8371,24 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>凤还巢</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>凤还巢</t>
+        </is>
+      </c>
       <c r="T94" t="n">
         <v>0</v>
       </c>
@@ -7741,24 +8453,30 @@
           <t>https://movie.douban.com/subject/27620588/</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>1938.428571428571</v>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>2017国剧盛典</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>2017国剧盛典</t>
+        </is>
+      </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -7821,16 +8539,24 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>寻找刘三姐</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>寻找刘三姐</t>
+        </is>
+      </c>
       <c r="T96" t="n">
         <v>0</v>
       </c>
@@ -7898,16 +8624,24 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>宋宫秘史</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>宋宫秘史</t>
+        </is>
+      </c>
       <c r="T97" t="n">
         <v>0</v>
       </c>
@@ -7975,16 +8709,24 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>歌迷小姐</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>歌迷小姐</t>
+        </is>
+      </c>
       <c r="T98" t="n">
         <v>0</v>
       </c>
@@ -8052,16 +8794,24 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>双凤奇缘</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>双凤奇缘</t>
+        </is>
+      </c>
       <c r="T99" t="n">
         <v>0</v>
       </c>
@@ -8129,16 +8879,24 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4189970412, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>跳舞吧！大象</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>跳舞吧！大象</t>
+        </is>
+      </c>
       <c r="T100" t="n">
         <v>0</v>
       </c>
@@ -8206,16 +8964,24 @@
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>潘金莲</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>潘金莲</t>
+        </is>
+      </c>
       <c r="T101" t="n">
         <v>0</v>
       </c>
@@ -8283,16 +9049,24 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>第三类打斗</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>第三类打斗</t>
+        </is>
+      </c>
       <c r="T102" t="n">
         <v>0</v>
       </c>
@@ -8360,16 +9134,24 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4190135910, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>梦圆东方2017东方卫视跨年盛典</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>梦圆东方2017东方卫视跨年盛典</t>
+        </is>
+      </c>
       <c r="T103" t="n">
         <v>0</v>
       </c>
@@ -8434,24 +9216,30 @@
           <t>https://movie.douban.com/subject/26985916/</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
+      <c r="O104" t="n">
+        <v>4223.428571428572</v>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>你美丽了我的人生</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>你美丽了我的人生</t>
+        </is>
+      </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -8514,16 +9302,24 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>花团锦簇</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>花团锦簇</t>
+        </is>
+      </c>
       <c r="T105" t="n">
         <v>0</v>
       </c>
@@ -8591,16 +9387,24 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>喷火美人鱼</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>喷火美人鱼</t>
+        </is>
+      </c>
       <c r="T106" t="n">
         <v>0</v>
       </c>
@@ -8665,24 +9469,30 @@
           <t>https://movie.douban.com/subject/26356172/</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>1171.714285714286</v>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>2015年中央电视台元宵晚会</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>2015年中央电视台元宵晚会</t>
+        </is>
+      </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -8745,16 +9555,24 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>缘邀知音</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>缘邀知音</t>
+        </is>
+      </c>
       <c r="T108" t="n">
         <v>0</v>
       </c>
@@ -8822,16 +9640,24 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>大盗歌王</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>大盗歌王</t>
+        </is>
+      </c>
       <c r="T109" t="n">
         <v>0</v>
       </c>
@@ -8896,24 +9722,30 @@
           <t>https://movie.douban.com/subject/26912454/</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>565.2857142857143</v>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>2016天猫双十一狂欢夜</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>2016天猫双十一狂欢夜</t>
+        </is>
+      </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U110" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -8976,16 +9808,24 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>红孩儿</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>红孩儿</t>
+        </is>
+      </c>
       <c r="T111" t="n">
         <v>0</v>
       </c>
@@ -9050,24 +9890,30 @@
           <t>https://movie.douban.com/subject/26921076/</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr"/>
+      <c r="O112" t="n">
+        <v>2771.571428571428</v>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>舞出我人生之舞所不能</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>舞出我人生之舞所不能</t>
+        </is>
+      </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -9130,16 +9976,24 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4191671834, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>2016年中央电视台元宵晚会</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>2016年中央电视台元宵晚会</t>
+        </is>
+      </c>
       <c r="T113" t="n">
         <v>0</v>
       </c>
@@ -9207,16 +10061,24 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4191852249, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>你咪理，我爱你！</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>你咪理，我爱你！</t>
+        </is>
+      </c>
       <c r="T114" t="n">
         <v>0</v>
       </c>
@@ -9284,16 +10146,24 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>歌舞青春</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>歌舞青春</t>
+        </is>
+      </c>
       <c r="T115" t="n">
         <v>0</v>
       </c>
@@ -9358,24 +10228,30 @@
           <t>https://movie.douban.com/subject/6963575/</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
+      <c r="O116" t="n">
+        <v>5541.714285714285</v>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>青春失乐园</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>青春失乐园</t>
+        </is>
+      </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -9438,16 +10314,24 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>七擒七纵七色狼</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>七擒七纵七色狼</t>
+        </is>
+      </c>
       <c r="T117" t="n">
         <v>0</v>
       </c>
@@ -9512,24 +10396,30 @@
           <t>https://movie.douban.com/subject/30295908/</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr"/>
+      <c r="O118" t="n">
+        <v>8504.714285714286</v>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>小猪佩奇过大年</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>小猪佩奇过大年</t>
+        </is>
+      </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -9589,24 +10479,30 @@
           <t>https://movie.douban.com/subject/35256235/</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
+      <c r="O119" t="n">
+        <v>8129.857142857143</v>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>燃野少年的天空</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>燃野少年的天空</t>
+        </is>
+      </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
@@ -9669,16 +10565,24 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4192974941, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>2017天猫双十一狂欢夜</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>2017天猫双十一狂欢夜</t>
+        </is>
+      </c>
       <c r="T120" t="n">
         <v>0</v>
       </c>
